--- a/resources/templates/standard/L1200-11.xlsx
+++ b/resources/templates/standard/L1200-11.xlsx
@@ -14,7 +14,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="16">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t xml:space="preserve">결
 재</t>
@@ -664,7 +667,9 @@
   </cols>
   <sheetData>
     <row r="1" ht="20.1" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="2"/>
@@ -703,15 +708,15 @@
       <c r="AK1" s="2"/>
       <c r="AL1" s="2"/>
       <c r="AM1" s="3" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN1" s="4" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO1" s="4"/>
       <c r="AP1" s="4"/>
       <c r="AQ1" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AR1" s="4"/>
       <c r="AS1" s="4"/>
@@ -812,7 +817,7 @@
     </row>
     <row r="4" ht="25.15" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -833,12 +838,12 @@
       <c r="R4" s="7"/>
       <c r="S4" s="7"/>
       <c r="T4" s="8" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U4" s="8"/>
       <c r="V4" s="8"/>
       <c r="W4" s="9" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X4" s="9"/>
       <c r="Y4" s="9"/>
@@ -887,7 +892,7 @@
       <c r="U5" s="8"/>
       <c r="V5" s="8"/>
       <c r="W5" s="10" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X5" s="10"/>
       <c r="Y5" s="10"/>
@@ -936,7 +941,7 @@
       <c r="U6" s="8"/>
       <c r="V6" s="8"/>
       <c r="W6" s="10" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X6" s="10"/>
       <c r="Y6" s="10"/>
@@ -985,7 +990,7 @@
       <c r="U7" s="8"/>
       <c r="V7" s="8"/>
       <c r="W7" s="10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X7" s="10"/>
       <c r="Y7" s="10"/>
@@ -1034,7 +1039,7 @@
       <c r="U8" s="8"/>
       <c r="V8" s="8"/>
       <c r="W8" s="10" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X8" s="10"/>
       <c r="Y8" s="10"/>
@@ -1083,7 +1088,7 @@
       <c r="U9" s="8"/>
       <c r="V9" s="8"/>
       <c r="W9" s="10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X9" s="10"/>
       <c r="Y9" s="10"/>
@@ -1132,7 +1137,7 @@
       <c r="U10" s="8"/>
       <c r="V10" s="8"/>
       <c r="W10" s="11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X10" s="11"/>
       <c r="Y10" s="11"/>
@@ -1159,7 +1164,7 @@
     </row>
     <row r="11" ht="18" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B11" s="12"/>
       <c r="C11" s="12"/>
@@ -1176,7 +1181,7 @@
       <c r="N11" s="13"/>
       <c r="O11" s="13"/>
       <c r="P11" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q11" s="13"/>
       <c r="R11" s="13"/>
@@ -1193,7 +1198,7 @@
       <c r="AC11" s="13"/>
       <c r="AD11" s="13"/>
       <c r="AE11" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AF11" s="13"/>
       <c r="AG11" s="13"/>
@@ -1266,7 +1271,7 @@
       <c r="F13" s="14"/>
       <c r="G13" s="14"/>
       <c r="H13" s="15" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I13" s="15"/>
       <c r="J13" s="15"/>
@@ -1283,7 +1288,7 @@
       <c r="U13" s="16"/>
       <c r="V13" s="16"/>
       <c r="W13" s="15" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="X13" s="15"/>
       <c r="Y13" s="15"/>
@@ -1300,7 +1305,7 @@
       <c r="AJ13" s="16"/>
       <c r="AK13" s="16"/>
       <c r="AL13" s="15" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AM13" s="15"/>
       <c r="AN13" s="15"/>
@@ -1413,7 +1418,7 @@
       <c r="F16" s="14"/>
       <c r="G16" s="14"/>
       <c r="H16" s="17" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I16" s="17"/>
       <c r="J16" s="17"/>
@@ -1430,7 +1435,7 @@
       <c r="U16" s="16"/>
       <c r="V16" s="16"/>
       <c r="W16" s="17" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="X16" s="17"/>
       <c r="Y16" s="17"/>
@@ -1447,7 +1452,7 @@
       <c r="AJ16" s="16"/>
       <c r="AK16" s="16"/>
       <c r="AL16" s="17" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AM16" s="17"/>
       <c r="AN16" s="17"/>
@@ -1553,7 +1558,7 @@
     </row>
     <row r="19" ht="18" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A19" s="19" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B19" s="19"/>
       <c r="C19" s="19"/>
@@ -1570,7 +1575,7 @@
       <c r="N19" s="20"/>
       <c r="O19" s="20"/>
       <c r="P19" s="20" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q19" s="20"/>
       <c r="R19" s="20"/>
@@ -1587,7 +1592,7 @@
       <c r="AC19" s="20"/>
       <c r="AD19" s="20"/>
       <c r="AE19" s="20" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AF19" s="20"/>
       <c r="AG19" s="20"/>
@@ -1660,7 +1665,7 @@
       <c r="F21" s="14"/>
       <c r="G21" s="14"/>
       <c r="H21" s="15" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I21" s="15"/>
       <c r="J21" s="15"/>
@@ -1677,7 +1682,7 @@
       <c r="U21" s="16"/>
       <c r="V21" s="16"/>
       <c r="W21" s="15" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="X21" s="15"/>
       <c r="Y21" s="15"/>
@@ -1694,7 +1699,7 @@
       <c r="AJ21" s="16"/>
       <c r="AK21" s="16"/>
       <c r="AL21" s="15" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AM21" s="15"/>
       <c r="AN21" s="15"/>
@@ -1807,7 +1812,7 @@
       <c r="F24" s="14"/>
       <c r="G24" s="14"/>
       <c r="H24" s="17" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I24" s="17"/>
       <c r="J24" s="17"/>
@@ -1824,7 +1829,7 @@
       <c r="U24" s="16"/>
       <c r="V24" s="16"/>
       <c r="W24" s="17" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="X24" s="17"/>
       <c r="Y24" s="17"/>
@@ -1841,7 +1846,7 @@
       <c r="AJ24" s="16"/>
       <c r="AK24" s="16"/>
       <c r="AL24" s="17" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AM24" s="17"/>
       <c r="AN24" s="17"/>
